--- a/runs/RELX/2026-10-14/bear/scratch/b_ronic_wacc/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_ronic_wacc/out/dcf.xlsx
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1100303133660505</v>
+        <v>0.1143111734818558</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PM rule: return on new investment 9.6% (value driver formula, briefs/RELX.yaml)</t>
+          <t>PM rule: return on new investment 8.9% (value driver formula, briefs/RELX.yaml)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2044.926705519653</v>
+        <v>2102.881781249673</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11133.7332424089</v>
+        <v>11302.6880463898</v>
       </c>
     </row>
     <row r="21">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2619.707524111502</v>
+        <v>2567.281824266467</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>34465.48052242755</v>
+        <v>37086.55672101786</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>22814.96038778523</v>
+        <v>25245.79238855498</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>33948.69363019413</v>
+        <v>36548.48043494478</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>26951.69363019413</v>
+        <v>29551.48043494478</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25833.38554860746</v>
+        <v>28464.46623573293</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.81480459872466</v>
+        <v>16.32366398495958</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1481.480459872466</v>
+        <v>1632.366398495958</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.465362519</v>
+        <v>-0.4109107187</v>
       </c>
     </row>
   </sheetData>
